--- a/菜品数据.xlsx
+++ b/菜品数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="菜品数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选菜记录" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计报表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="菜品数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="选菜记录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="统计报表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'菜品数据'!$A$1:$H$26</definedName>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1376,10 +1376,117 @@
 3.空气炸锅180度15分钟即可</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>花菜</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>闷烧丝瓜</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>素菜</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>丝瓜</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.丝瓜切滚刀块，放入锅中
+2.分别放入蒜油、虾米、酱油、蚝油、一点清水
+3.扣上锅盖，中小火焖5分钟</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>丝瓜1根、蒜油适量、虾米少许、酱油1勺、蚝油1勺、清水适量</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>玉带丝瓜</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>素菜</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>丝瓜，虾仁</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1.炖锅底部放油，蒜瓣铺满锅底，放入两片姜，爆炒至蒜米金黄，取走姜片
+2.放入丝瓜条，撒上盐，盖上锅盖小火焖2分钟
+3.打开翻丝瓜条，再焖2分钟
+4.水焖出来后下入焯过水的虾仁，撒味精和胡椒粉拌匀
+5.大火煮一点水即可上桌</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>丝瓜1根、虾仁适量、蒜瓣适量、姜2片、盐适量、味精少许、胡椒粉少许</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>肉末粉丝煲</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>荤菜</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>肉末，粉丝</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>肉末适量、粉丝1把</t>
         </is>
       </c>
     </row>
@@ -1630,18 +1737,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1676,7 +1773,6 @@
           <t>菜品数量</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>分类</t>
@@ -1687,7 +1783,6 @@
           <t>菜品数量</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="inlineStr">
         <is>
           <t>菜品名称</t>
@@ -1714,7 +1809,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1733,7 +1828,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1768,7 +1863,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1787,7 +1882,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1852,7 +1947,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2059,6 +2154,39 @@
       </c>
       <c r="H27">
         <f>COUNTIF(选菜记录!$D:$D,G27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>闷烧丝瓜</t>
+        </is>
+      </c>
+      <c r="H28">
+        <f>COUNTIF(选菜记录!$D:$D,G28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>玉带丝瓜</t>
+        </is>
+      </c>
+      <c r="H29">
+        <f>COUNTIF(选菜记录!$D:$D,G29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>肉末粉丝煲</t>
+        </is>
+      </c>
+      <c r="H30">
+        <f>COUNTIF(选菜记录!$D:$D,G30)</f>
         <v/>
       </c>
     </row>

--- a/菜品数据.xlsx
+++ b/菜品数据.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1482,11 +1482,47 @@
           <t>肉末，粉丝</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>肉末适量、粉丝1把</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>炒方便面</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>主食</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>方便面饼，火腿肠，包菜，洋葱，绿豆芽，鸡蛋，蒜末</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>一、准备食材：主料2块方便面饼；配菜火腿肠、包菜、洋葱、绿豆芽；配料鸡蛋、蒜末；料汁2勺生抽、半勺老抽、1勺香油、1勺辣椒面、少许十三香、少许鸡精。
+二、处理面条：1.锅中水烧开，放入方便面饼煮至7分熟 2.捞出沥干水分，放入大盆 3.往面条喷少许油，用筷子挑开放凉备用。
+三、炒制：1.起锅烧油，倒入蛋液炒散盛出 2.锅中留底油，放入火腿肠片翻炒均匀 3.加蒜末煸出香味 4.放入包菜、洋葱、绿豆芽炒至稍微发软 5.倒入放凉的方便面，加料汁快速翻炒均匀 6.炒至熟透入味即可出锅装盘</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>方便面饼2块、火腿肠1根、包菜适量、洋葱适量、绿豆芽适量、鸡蛋1个、蒜末适量、生抽2勺、老抽半勺、香油1勺、辣椒面1勺、十三香少许、鸡精少许</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,7 +1864,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1836,7 +1872,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1882,7 +1918,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1947,7 +1983,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2187,6 +2223,17 @@
       </c>
       <c r="H30">
         <f>COUNTIF(选菜记录!$D:$D,G30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>炒方便面</t>
+        </is>
+      </c>
+      <c r="H31">
+        <f>COUNTIF(选菜记录!$D:$D,G31)</f>
         <v/>
       </c>
     </row>

--- a/菜品数据.xlsx
+++ b/菜品数据.xlsx
@@ -38,31 +38,26 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
       <family val="3"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3E6"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -77,16 +72,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -453,12 +444,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -467,42 +458,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>菜品名称</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>餐次</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>食材（原料）</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>菜谱步骤</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>抖音链接</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>食材清单</t>
         </is>
@@ -564,7 +555,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>德芙巧克力</t>
+          <t>巧克力</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1084,7 +1075,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>儿菜，小辣椒</t>
+          <t>儿菜，辣椒</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1119,7 +1110,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>面粉，鸡蛋，小葱</t>
+          <t>面粉，鸡蛋</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1154,7 +1145,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>春笋/茭白</t>
+          <t>春笋,茭白</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1189,7 +1180,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>鸡蛋，冰红茶，红烧牛肉面调料包</t>
+          <t>鸡蛋，冰红茶</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1224,7 +1215,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>丝瓜，蒜</t>
+          <t>丝瓜</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1509,7 +1500,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>方便面饼，火腿肠，包菜，洋葱，绿豆芽，鸡蛋，蒜末</t>
+          <t>方便面饼，火腿肠，包菜，洋葱，绿豆芽，鸡蛋</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1519,10 +1510,51 @@
 三、炒制：1.起锅烧油，倒入蛋液炒散盛出 2.锅中留底油，放入火腿肠片翻炒均匀 3.加蒜末煸出香味 4.放入包菜、洋葱、绿豆芽炒至稍微发软 5.倒入放凉的方便面，加料汁快速翻炒均匀 6.炒至熟透入味即可出锅装盘</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>方便面饼2块、火腿肠1根、包菜适量、洋葱适量、绿豆芽适量、鸡蛋1个、蒜末适量、生抽2勺、老抽半勺、香油1勺、辣椒面1勺、十三香少许、鸡精少许</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>家常粉蒸肉</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>荤菜</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>五花肉，米粉，南瓜，豆瓣酱，生抽，鸡精，葱花</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.备料腌制：五花肉依次加入豆瓣酱、生抽、鸡精，再放入200克米粉，少量多次加清水，抓拌至每片肉都裹上粉，腌制20分钟
+2.摆盘蒸制：盘中铺南瓜片打底，均匀铺上腌制好的肉片，放入蒸锅，水开后转小火蒸60分钟
+3.完成出锅：蒸好后撒上葱花即可，口感软糯鲜嫩</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://v.douyin.com/NO17qN0u2ko/</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>五花肉适量、米粉200克、南瓜适量、豆瓣酱适量、生抽少许、鸡精少许、葱花少许</t>
         </is>
       </c>
     </row>
@@ -1773,58 +1805,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>各餐次菜品数量</t>
         </is>
       </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>各分类菜品数量</t>
         </is>
       </c>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>菜品被选次数</t>
         </is>
       </c>
-      <c r="H1" s="5" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>餐次</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>菜品数量</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>菜品数量</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>菜品名称</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>被选次数</t>
         </is>
@@ -1864,7 +1896,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1899,7 +1931,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1918,7 +1950,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1983,7 +2015,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2234,6 +2266,17 @@
       </c>
       <c r="H31">
         <f>COUNTIF(选菜记录!$D:$D,G31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>家常粉蒸肉</t>
+        </is>
+      </c>
+      <c r="H32">
+        <f>COUNTIF(选菜记录!$D:$D,G32)</f>
         <v/>
       </c>
     </row>

--- a/菜品数据.xlsx
+++ b/菜品数据.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1555,6 +1555,47 @@
       <c r="H31" t="inlineStr">
         <is>
           <t>五花肉适量、米粉200克、南瓜适量、豆瓣酱适量、生抽少许、鸡精少许、葱花少许</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>丝瓜滑肉汤</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>汤</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>丝瓜，肉片，红薯淀粉，姜，葱，香油</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>一、丝瓜翠绿不发黑关键：1.丝瓜切块后用加盐的清水浸泡 2.炒丝瓜时先炒软再加水，避免长时间高温炖煮。
+二、制作步骤：1.丝瓜处理：切块，放入加一勺盐的清水中浸泡，炒后翠绿不发黑 2.肉片腌制：加盐、胡椒粉、葱姜水抓匀腌制；加等量红薯淀粉抓拌均匀；分次加入开水，揉至肉片上浆粘稠 3.炒制：锅中放少量菜油+猪油，下姜丝爆香；捞出沥干的丝瓜下锅炒至微软；加适量清水，水开后转文火；肉片依次下锅，中途不要翻动，煮至肉片透明 4.调味出锅：加盐、味精、胡椒粉调味，出锅前加葱花、滴少许香油，轻微翻动后盛出</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://v.douyin.com/QbX5vabWxvQ/</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>丝瓜1根、肉片适量、盐适量、胡椒粉少许、葱姜水适量、红薯淀粉适量、菜油少许、猪油少许、姜丝适量、味精少许、香油少许、葱花适量</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1896,7 +1937,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1950,7 +1991,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1977,7 +2018,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2015,7 +2056,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2277,6 +2318,17 @@
       </c>
       <c r="H32">
         <f>COUNTIF(选菜记录!$D:$D,G32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>丝瓜滑肉汤</t>
+        </is>
+      </c>
+      <c r="H33">
+        <f>COUNTIF(选菜记录!$D:$D,G33)</f>
         <v/>
       </c>
     </row>

--- a/菜品数据.xlsx
+++ b/菜品数据.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1596,6 +1596,44 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>丝瓜1根、肉片适量、盐适量、胡椒粉少许、葱姜水适量、红薯淀粉适量、菜油少许、猪油少许、姜丝适量、味精少许、香油少许、葱花适量</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>空气炸锅香辣烤豆腐</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>素菜</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>内酯豆腐，鸡蛋，蒜末，小米辣，葱花</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>一、基础准备：食材：内酯豆腐1盒、鸡蛋1个、蒜末、小米辣、葱花；调料：盐、辣椒面、生抽、老抽、食用油；工具：空气炸锅、锡纸盘。
+二、分步制作：1.豆腐预处理：内酯豆腐倒入锡纸盘，捣碎铺平，淋上打散的鸡蛋液 2.第一次烤制：空气炸锅170℃烤10分钟定型 3.制作香辣料汁：碗中放蒜末、小米辣、1勺盐、1大勺辣椒面、1勺生抽、1勺老抽，淋热油激香搅匀 4.二次烤制：料汁均匀铺在烤好的豆腐上，边角都覆盖，160℃再烤8分钟 5.收尾出锅：撒葱花即可食用。
+三、关键提示：内酯豆腐质地软嫩，烤后外焦里嫩，鸡蛋液增加风味层次；空气炸锅温度时间可依设备调整，避免烤糊；不吃辣可减少小米辣和辣椒面用量，喜酱香可加少许蚝油。</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>内酯豆腐1盒、鸡蛋1个、蒜末适量、小米辣适量、葱花适量、盐1勺、辣椒面1大勺、生抽1勺、老抽1勺、食用油适量</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1918,7 +1956,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1937,7 +1975,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1991,7 +2029,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2056,7 +2094,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2329,6 +2367,17 @@
       </c>
       <c r="H33">
         <f>COUNTIF(选菜记录!$D:$D,G33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>空气炸锅香辣烤豆腐</t>
+        </is>
+      </c>
+      <c r="H34">
+        <f>COUNTIF(选菜记录!$D:$D,G34)</f>
         <v/>
       </c>
     </row>

--- a/菜品数据.xlsx
+++ b/菜品数据.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1630,10 +1630,49 @@
 三、关键提示：内酯豆腐质地软嫩，烤后外焦里嫩，鸡蛋液增加风味层次；空气炸锅温度时间可依设备调整，避免烤糊；不吃辣可减少小米辣和辣椒面用量，喜酱香可加少许蚝油。</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>内酯豆腐1盒、鸡蛋1个、蒜末适量、小米辣适量、葱花适量、盐1勺、辣椒面1大勺、生抽1勺、老抽1勺、食用油适量</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>红烧冬瓜</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>正餐</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>素菜</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>冬瓜，大蒜</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.切冬瓜：尽量选黑皮冬瓜，皮切薄一点、多留厚的冬瓜皮肉，切成块后把瓤扔掉。
+2.锅中放足够多的水没过冬瓜块，同时放入两块大蒜头。
+3.放一个八角、一个桂皮、两勺生抽、一勺老抽、一点盐，再加冰糖、蚝油，最后放一点猪油（关键）。
+4.大火烧开后转中小火烧15到20分钟，把水尽量烧干，再加一点土豆粉或生粉勾芡。
+5.最后撒一点香葱出锅。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>冬瓜1个、大蒜头2块、八角1个、桂皮1个、生抽2勺、老抽1勺、盐少许、冰糖适量、蚝油适量、猪油少许、土豆粉或生粉适量、香葱少许</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1956,7 +1995,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1975,7 +2014,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2029,7 +2068,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2094,7 +2133,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2378,6 +2417,17 @@
       </c>
       <c r="H34">
         <f>COUNTIF(选菜记录!$D:$D,G34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>红烧冬瓜</t>
+        </is>
+      </c>
+      <c r="H35">
+        <f>COUNTIF(选菜记录!$D:$D,G35)</f>
         <v/>
       </c>
     </row>
